--- a/App_Data/GoldRates/GoldRates.xlsx
+++ b/App_Data/GoldRates/GoldRates.xlsx
@@ -581,6 +581,27 @@
   </x:si>
   <x:si>
     <x:t>15:34:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16:15:51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27-09-2026 16:15:50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16:15:55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16:16:42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27-09-2026 16:16:41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16:19:34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27-09-2026 16:19:33</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -10167,6 +10188,426 @@
         <x:v>19</x:v>
       </x:c>
     </x:row>
+    <x:row r="264" spans="1:11">
+      <x:c r="A264" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B264" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="C264" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D264" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E264" s="0">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F264" s="0">
+        <x:v>173.2</x:v>
+      </x:c>
+      <x:c r="G264" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H264" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I264" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="J264" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K264" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" spans="1:11">
+      <x:c r="A265" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B265" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="C265" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D265" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E265" s="0">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="F265" s="0">
+        <x:v>188.1</x:v>
+      </x:c>
+      <x:c r="G265" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H265" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I265" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="J265" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K265" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" spans="1:11">
+      <x:c r="A266" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B266" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C266" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D266" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E266" s="0">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F266" s="0">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G266" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H266" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I266" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="J266" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K266" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" spans="1:11">
+      <x:c r="A267" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B267" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C267" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D267" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E267" s="0">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="F267" s="0">
+        <x:v>184.7</x:v>
+      </x:c>
+      <x:c r="G267" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H267" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I267" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="J267" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K267" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" spans="1:11">
+      <x:c r="A268" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B268" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C268" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D268" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E268" s="0">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F268" s="0">
+        <x:v>173.2</x:v>
+      </x:c>
+      <x:c r="G268" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H268" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I268" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="J268" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K268" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" spans="1:11">
+      <x:c r="A269" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B269" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C269" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D269" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E269" s="0">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="F269" s="0">
+        <x:v>188.1</x:v>
+      </x:c>
+      <x:c r="G269" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H269" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I269" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="J269" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K269" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" spans="1:11">
+      <x:c r="A270" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B270" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C270" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D270" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E270" s="0">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F270" s="0">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G270" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H270" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I270" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="J270" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K270" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" spans="1:11">
+      <x:c r="A271" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B271" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C271" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D271" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E271" s="0">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="F271" s="0">
+        <x:v>184.7</x:v>
+      </x:c>
+      <x:c r="G271" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H271" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I271" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="J271" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K271" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" spans="1:11">
+      <x:c r="A272" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B272" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C272" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D272" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E272" s="0">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F272" s="0">
+        <x:v>173.2</x:v>
+      </x:c>
+      <x:c r="G272" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H272" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I272" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J272" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K272" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" spans="1:11">
+      <x:c r="A273" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B273" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C273" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D273" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E273" s="0">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="F273" s="0">
+        <x:v>188.1</x:v>
+      </x:c>
+      <x:c r="G273" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H273" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I273" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J273" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K273" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" spans="1:11">
+      <x:c r="A274" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B274" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C274" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D274" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E274" s="0">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F274" s="0">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G274" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H274" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I274" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J274" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K274" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" spans="1:11">
+      <x:c r="A275" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B275" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C275" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D275" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E275" s="0">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="F275" s="0">
+        <x:v>184.7</x:v>
+      </x:c>
+      <x:c r="G275" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H275" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I275" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J275" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K275" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/App_Data/GoldRates/GoldRates.xlsx
+++ b/App_Data/GoldRates/GoldRates.xlsx
@@ -602,6 +602,21 @@
   </x:si>
   <x:si>
     <x:t>27-09-2026 16:19:33</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16:38:11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27-09-2026 16:38:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16:38:14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16:40:11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27-09-2026 16:40:09</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -10608,6 +10623,286 @@
         <x:v>19</x:v>
       </x:c>
     </x:row>
+    <x:row r="276" spans="1:11">
+      <x:c r="A276" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B276" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C276" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D276" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E276" s="0">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F276" s="0">
+        <x:v>173.2</x:v>
+      </x:c>
+      <x:c r="G276" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H276" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I276" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="J276" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K276" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" spans="1:11">
+      <x:c r="A277" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B277" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="C277" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D277" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E277" s="0">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="F277" s="0">
+        <x:v>188.1</x:v>
+      </x:c>
+      <x:c r="G277" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H277" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I277" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="J277" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K277" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" spans="1:11">
+      <x:c r="A278" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B278" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C278" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D278" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E278" s="0">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F278" s="0">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G278" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H278" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I278" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="J278" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K278" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" spans="1:11">
+      <x:c r="A279" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B279" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C279" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D279" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E279" s="0">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="F279" s="0">
+        <x:v>184.7</x:v>
+      </x:c>
+      <x:c r="G279" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H279" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I279" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="J279" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K279" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" spans="1:11">
+      <x:c r="A280" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B280" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C280" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D280" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E280" s="0">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F280" s="0">
+        <x:v>173.2</x:v>
+      </x:c>
+      <x:c r="G280" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H280" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I280" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J280" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K280" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:11">
+      <x:c r="A281" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B281" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C281" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D281" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E281" s="0">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="F281" s="0">
+        <x:v>188.1</x:v>
+      </x:c>
+      <x:c r="G281" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H281" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I281" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J281" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K281" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" spans="1:11">
+      <x:c r="A282" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B282" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C282" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D282" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E282" s="0">
+        <x:v>916</x:v>
+      </x:c>
+      <x:c r="F282" s="0">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G282" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H282" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I282" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J282" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K282" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:11">
+      <x:c r="A283" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B283" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="C283" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D283" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E283" s="0">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="F283" s="0">
+        <x:v>184.7</x:v>
+      </x:c>
+      <x:c r="G283" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H283" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I283" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J283" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K283" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
